--- a/product_surveys/007_platform_user_experience_survey--product_surveys.xlsx
+++ b/product_surveys/007_platform_user_experience_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>What is your experience with our platform?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,40 +538,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_2</t>
+          <t>user_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>How satisfied are you with the platform?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_3</t>
+          <t>product_improvement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>product_improvement</t>
+          <t>What features would you like to see added or improved?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_4</t>
+          <t>issue_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>issue_description</t>
+          <t>Describe any issues you've encountered with the platform</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_5</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Do you have any feedback or suggestions for the platform?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_6</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is your email address and phone number?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_7</t>
+          <t>preferred_channel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Do you prefer to communicate through email, in-app, phone, or other?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8</t>
+          <t>other_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>preferred_channel</t>
+          <t>Do you have any other comments or details to share?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_9</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>other_info</t>
+          <t>Is there anything else you'd like to add or comment on?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,63 +722,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_10</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>What are your final thoughts on the platform?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_11</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>survey_conclusion</t>
+          <t>Have you read and understood the terms and conditions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_12</t>
+          <t>date_completed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>What date did you complete this survey?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_13</t>
+          <t>time_completed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey</t>
+          <t>What time did you complete this survey?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,92 +814,92 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_14</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>How would you rate the platform overall?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_15</t>
+          <t>platform_experience</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Describe your overall experience with the platform?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_16</t>
+          <t>platform_contact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey</t>
+          <t>What is your preferred method of contact (email, in-app, phone, etc.)?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_17</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey</t>
+          <t>Do you have any additional comments or thoughts?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_18</t>
+          <t>final_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey</t>
+          <t>Are there any final comments or thoughts you'd like to add?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,323 +965,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_3_choices</t>
+          <t>user_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_3_choices</t>
+          <t>user_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_3_choices</t>
+          <t>user_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_app'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'in_app'}</t>
+          <t>In-App</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8_choices</t>
+          <t>preferred_channel_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'inperson'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'inperson'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_8_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_13_choices</t>
+          <t>terms_and_conditions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_13_choices</t>
+          <t>platform_contact_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_13_choices</t>
+          <t>platform_contact_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe'}</t>
+          <t>In-App</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_17_choices</t>
+          <t>platform_contact_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option_1'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>platform_user_experience_survey_page_17_choices</t>
+          <t>platform_contact_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option_2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'option_3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'option_4'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'option_4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'name':_'option_5'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'name': 'option_5'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'option_1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'option_2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>platform_user_experience_survey_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'option_3'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
